--- a/reports/Data_Dictionary_Template.xlsx
+++ b/reports/Data_Dictionary_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8dd09a5e522366ce/Documents/Project_3.1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="639" documentId="8_{CC3B83E4-4774-4DEE-8C1A-6012C9DA1E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83F8C8C9-0B11-45FB-AECE-1FE3B5A95AB2}"/>
+  <xr:revisionPtr revIDLastSave="635" documentId="8_{CC3B83E4-4774-4DEE-8C1A-6012C9DA1E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2822133C-CFD8-478F-8A21-6BA7C735745F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="405">
   <si>
     <t>Data Dictionary — Preparation Template</t>
   </si>
@@ -1264,9 +1264,6 @@
   </si>
   <si>
     <t>Table containing 1,212 rows of IPL matches data.</t>
-  </si>
-  <si>
-    <t>primary Key</t>
   </si>
 </sst>
 </file>
@@ -1611,18 +1608,18 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2177,81 +2174,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="21">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="45"/>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="45"/>
-      <c r="S1" s="45"/>
-      <c r="T1" s="45"/>
-      <c r="U1" s="45"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="40"/>
+      <c r="Q1" s="40"/>
+      <c r="R1" s="40"/>
+      <c r="S1" s="40"/>
+      <c r="T1" s="40"/>
+      <c r="U1" s="40"/>
     </row>
     <row r="2" spans="1:33">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
-      <c r="O2" s="46"/>
-      <c r="P2" s="46"/>
-      <c r="Q2" s="46"/>
-      <c r="R2" s="46"/>
-      <c r="S2" s="46"/>
-      <c r="T2" s="46"/>
-      <c r="U2" s="46"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="41"/>
+      <c r="P2" s="41"/>
+      <c r="Q2" s="41"/>
+      <c r="R2" s="41"/>
+      <c r="S2" s="41"/>
+      <c r="T2" s="41"/>
+      <c r="U2" s="41"/>
     </row>
     <row r="4" spans="1:33" ht="15" customHeight="1">
       <c r="A4" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="41" t="s">
+      <c r="B4" s="39" t="s">
         <v>122</v>
       </c>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="41"/>
-      <c r="L4" s="41"/>
-      <c r="M4" s="41"/>
-      <c r="N4" s="41"/>
-      <c r="O4" s="41"/>
-      <c r="P4" s="41"/>
-      <c r="Q4" s="41"/>
-      <c r="R4" s="41"/>
-      <c r="S4" s="41"/>
-      <c r="T4" s="41"/>
-      <c r="U4" s="41"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="39"/>
+      <c r="M4" s="39"/>
+      <c r="N4" s="39"/>
+      <c r="O4" s="39"/>
+      <c r="P4" s="39"/>
+      <c r="Q4" s="39"/>
+      <c r="R4" s="39"/>
+      <c r="S4" s="39"/>
+      <c r="T4" s="39"/>
+      <c r="U4" s="39"/>
     </row>
     <row r="5" spans="1:33" ht="15" customHeight="1">
       <c r="A5" s="13" t="s">
@@ -2290,26 +2287,26 @@
       <c r="C6" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D6" s="44" t="s">
+      <c r="D6" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="44"/>
-      <c r="N6" s="44"/>
-      <c r="O6" s="44"/>
-      <c r="P6" s="44"/>
-      <c r="Q6" s="44"/>
-      <c r="R6" s="44"/>
-      <c r="S6" s="44"/>
-      <c r="T6" s="44"/>
-      <c r="U6" s="44"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="42"/>
+      <c r="L6" s="42"/>
+      <c r="M6" s="42"/>
+      <c r="N6" s="42"/>
+      <c r="O6" s="42"/>
+      <c r="P6" s="42"/>
+      <c r="Q6" s="42"/>
+      <c r="R6" s="42"/>
+      <c r="S6" s="42"/>
+      <c r="T6" s="42"/>
+      <c r="U6" s="42"/>
     </row>
     <row r="7" spans="1:33" ht="15" customHeight="1" thickBot="1">
       <c r="A7" s="13"/>
@@ -2344,28 +2341,28 @@
       <c r="A8" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="41" t="s">
+      <c r="B8" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="41"/>
-      <c r="K8" s="41"/>
-      <c r="L8" s="41"/>
-      <c r="M8" s="41"/>
-      <c r="N8" s="41"/>
-      <c r="O8" s="41"/>
-      <c r="P8" s="41"/>
-      <c r="Q8" s="41"/>
-      <c r="R8" s="41"/>
-      <c r="S8" s="41"/>
-      <c r="T8" s="41"/>
-      <c r="U8" s="41"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
+      <c r="K8" s="39"/>
+      <c r="L8" s="39"/>
+      <c r="M8" s="39"/>
+      <c r="N8" s="39"/>
+      <c r="O8" s="39"/>
+      <c r="P8" s="39"/>
+      <c r="Q8" s="39"/>
+      <c r="R8" s="39"/>
+      <c r="S8" s="39"/>
+      <c r="T8" s="39"/>
+      <c r="U8" s="39"/>
     </row>
     <row r="9" spans="1:33" ht="15" customHeight="1">
       <c r="A9" s="15" t="s">
@@ -2754,7 +2751,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:33" ht="26.4">
+    <row r="16" spans="1:33">
       <c r="A16" s="19" t="s">
         <v>72</v>
       </c>
@@ -2762,7 +2759,7 @@
         <v>75</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D16" s="21" t="s">
         <v>74</v>
@@ -2774,10 +2771,10 @@
         <v>74</v>
       </c>
       <c r="G16" s="21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H16" s="21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I16" s="21" t="s">
         <v>74</v>
@@ -2840,7 +2837,7 @@
         <v>74</v>
       </c>
       <c r="AC16" s="34" t="s">
-        <v>405</v>
+        <v>74</v>
       </c>
       <c r="AD16" s="34" t="s">
         <v>75</v>
@@ -3367,28 +3364,28 @@
       <c r="A26" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="B26" s="41" t="s">
+      <c r="B26" s="39" t="s">
         <v>400</v>
       </c>
-      <c r="C26" s="42"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="42"/>
-      <c r="I26" s="42"/>
-      <c r="J26" s="42"/>
-      <c r="K26" s="42"/>
-      <c r="L26" s="42"/>
-      <c r="M26" s="42"/>
-      <c r="N26" s="42"/>
-      <c r="O26" s="42"/>
-      <c r="P26" s="42"/>
-      <c r="Q26" s="42"/>
-      <c r="R26" s="42"/>
-      <c r="S26" s="42"/>
-      <c r="T26" s="42"/>
-      <c r="U26" s="43"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="43"/>
+      <c r="L26" s="43"/>
+      <c r="M26" s="43"/>
+      <c r="N26" s="43"/>
+      <c r="O26" s="43"/>
+      <c r="P26" s="43"/>
+      <c r="Q26" s="43"/>
+      <c r="R26" s="43"/>
+      <c r="S26" s="43"/>
+      <c r="T26" s="43"/>
+      <c r="U26" s="44"/>
     </row>
     <row r="27" spans="1:33" ht="14.4" customHeight="1">
       <c r="A27" s="13" t="s">
@@ -3397,25 +3394,25 @@
       <c r="B27" s="38" t="s">
         <v>401</v>
       </c>
-      <c r="C27" s="39"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="39"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="39"/>
-      <c r="J27" s="39"/>
-      <c r="K27" s="39"/>
-      <c r="L27" s="39"/>
-      <c r="M27" s="39"/>
-      <c r="N27" s="39"/>
-      <c r="O27" s="39"/>
-      <c r="P27" s="39"/>
-      <c r="Q27" s="39"/>
-      <c r="R27" s="39"/>
-      <c r="S27" s="39"/>
-      <c r="T27" s="39"/>
-      <c r="U27" s="40"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="45"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="45"/>
+      <c r="M27" s="45"/>
+      <c r="N27" s="45"/>
+      <c r="O27" s="45"/>
+      <c r="P27" s="45"/>
+      <c r="Q27" s="45"/>
+      <c r="R27" s="45"/>
+      <c r="S27" s="45"/>
+      <c r="T27" s="45"/>
+      <c r="U27" s="46"/>
     </row>
     <row r="28" spans="1:33">
       <c r="A28" s="13" t="s">
@@ -3427,26 +3424,26 @@
       <c r="C28" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D28" s="44" t="s">
+      <c r="D28" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="E28" s="39"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="39"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="39"/>
-      <c r="K28" s="39"/>
-      <c r="L28" s="39"/>
-      <c r="M28" s="39"/>
-      <c r="N28" s="39"/>
-      <c r="O28" s="39"/>
-      <c r="P28" s="39"/>
-      <c r="Q28" s="39"/>
-      <c r="R28" s="39"/>
-      <c r="S28" s="39"/>
-      <c r="T28" s="39"/>
-      <c r="U28" s="40"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="45"/>
+      <c r="H28" s="45"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="45"/>
+      <c r="K28" s="45"/>
+      <c r="L28" s="45"/>
+      <c r="M28" s="45"/>
+      <c r="N28" s="45"/>
+      <c r="O28" s="45"/>
+      <c r="P28" s="45"/>
+      <c r="Q28" s="45"/>
+      <c r="R28" s="45"/>
+      <c r="S28" s="45"/>
+      <c r="T28" s="45"/>
+      <c r="U28" s="46"/>
     </row>
     <row r="29" spans="1:33" ht="15" customHeight="1" thickBot="1">
       <c r="A29" s="13"/>
@@ -3459,50 +3456,50 @@
       <c r="D29" s="38" t="s">
         <v>345</v>
       </c>
-      <c r="E29" s="39"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="39"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="39"/>
-      <c r="J29" s="39"/>
-      <c r="K29" s="39"/>
-      <c r="L29" s="39"/>
-      <c r="M29" s="39"/>
-      <c r="N29" s="39"/>
-      <c r="O29" s="39"/>
-      <c r="P29" s="39"/>
-      <c r="Q29" s="39"/>
-      <c r="R29" s="39"/>
-      <c r="S29" s="39"/>
-      <c r="T29" s="39"/>
-      <c r="U29" s="40"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="45"/>
+      <c r="H29" s="45"/>
+      <c r="I29" s="45"/>
+      <c r="J29" s="45"/>
+      <c r="K29" s="45"/>
+      <c r="L29" s="45"/>
+      <c r="M29" s="45"/>
+      <c r="N29" s="45"/>
+      <c r="O29" s="45"/>
+      <c r="P29" s="45"/>
+      <c r="Q29" s="45"/>
+      <c r="R29" s="45"/>
+      <c r="S29" s="45"/>
+      <c r="T29" s="45"/>
+      <c r="U29" s="46"/>
     </row>
     <row r="30" spans="1:33">
       <c r="A30" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B30" s="41" t="s">
+      <c r="B30" s="39" t="s">
         <v>403</v>
       </c>
-      <c r="C30" s="42"/>
-      <c r="D30" s="42"/>
-      <c r="E30" s="42"/>
-      <c r="F30" s="42"/>
-      <c r="G30" s="42"/>
-      <c r="H30" s="42"/>
-      <c r="I30" s="42"/>
-      <c r="J30" s="42"/>
-      <c r="K30" s="42"/>
-      <c r="L30" s="42"/>
-      <c r="M30" s="42"/>
-      <c r="N30" s="42"/>
-      <c r="O30" s="42"/>
-      <c r="P30" s="42"/>
-      <c r="Q30" s="42"/>
-      <c r="R30" s="42"/>
-      <c r="S30" s="42"/>
-      <c r="T30" s="42"/>
-      <c r="U30" s="43"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
+      <c r="L30" s="43"/>
+      <c r="M30" s="43"/>
+      <c r="N30" s="43"/>
+      <c r="O30" s="43"/>
+      <c r="P30" s="43"/>
+      <c r="Q30" s="43"/>
+      <c r="R30" s="43"/>
+      <c r="S30" s="43"/>
+      <c r="T30" s="43"/>
+      <c r="U30" s="44"/>
     </row>
     <row r="31" spans="1:33" ht="14.4" customHeight="1">
       <c r="A31" s="15" t="s">
@@ -3511,25 +3508,25 @@
       <c r="B31" s="38" t="s">
         <v>404</v>
       </c>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="39"/>
-      <c r="G31" s="39"/>
-      <c r="H31" s="39"/>
-      <c r="I31" s="39"/>
-      <c r="J31" s="39"/>
-      <c r="K31" s="39"/>
-      <c r="L31" s="39"/>
-      <c r="M31" s="39"/>
-      <c r="N31" s="39"/>
-      <c r="O31" s="39"/>
-      <c r="P31" s="39"/>
-      <c r="Q31" s="39"/>
-      <c r="R31" s="39"/>
-      <c r="S31" s="39"/>
-      <c r="T31" s="39"/>
-      <c r="U31" s="40"/>
+      <c r="C31" s="45"/>
+      <c r="D31" s="45"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="45"/>
+      <c r="G31" s="45"/>
+      <c r="H31" s="45"/>
+      <c r="I31" s="45"/>
+      <c r="J31" s="45"/>
+      <c r="K31" s="45"/>
+      <c r="L31" s="45"/>
+      <c r="M31" s="45"/>
+      <c r="N31" s="45"/>
+      <c r="O31" s="45"/>
+      <c r="P31" s="45"/>
+      <c r="Q31" s="45"/>
+      <c r="R31" s="45"/>
+      <c r="S31" s="45"/>
+      <c r="T31" s="45"/>
+      <c r="U31" s="46"/>
     </row>
     <row r="32" spans="1:33">
       <c r="A32" s="15" t="s">
@@ -4393,28 +4390,28 @@
       <c r="A47" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="B47" s="41" t="s">
+      <c r="B47" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="C47" s="42"/>
-      <c r="D47" s="42"/>
-      <c r="E47" s="42"/>
-      <c r="F47" s="42"/>
-      <c r="G47" s="42"/>
-      <c r="H47" s="42"/>
-      <c r="I47" s="42"/>
-      <c r="J47" s="42"/>
-      <c r="K47" s="42"/>
-      <c r="L47" s="42"/>
-      <c r="M47" s="42"/>
-      <c r="N47" s="42"/>
-      <c r="O47" s="42"/>
-      <c r="P47" s="42"/>
-      <c r="Q47" s="42"/>
-      <c r="R47" s="42"/>
-      <c r="S47" s="42"/>
-      <c r="T47" s="42"/>
-      <c r="U47" s="43"/>
+      <c r="C47" s="43"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="43"/>
+      <c r="F47" s="43"/>
+      <c r="G47" s="43"/>
+      <c r="H47" s="43"/>
+      <c r="I47" s="43"/>
+      <c r="J47" s="43"/>
+      <c r="K47" s="43"/>
+      <c r="L47" s="43"/>
+      <c r="M47" s="43"/>
+      <c r="N47" s="43"/>
+      <c r="O47" s="43"/>
+      <c r="P47" s="43"/>
+      <c r="Q47" s="43"/>
+      <c r="R47" s="43"/>
+      <c r="S47" s="43"/>
+      <c r="T47" s="43"/>
+      <c r="U47" s="44"/>
     </row>
     <row r="48" spans="1:29">
       <c r="A48" s="13" t="s">
@@ -4423,25 +4420,25 @@
       <c r="B48" s="38" t="s">
         <v>342</v>
       </c>
-      <c r="C48" s="39"/>
-      <c r="D48" s="39"/>
-      <c r="E48" s="39"/>
-      <c r="F48" s="39"/>
-      <c r="G48" s="39"/>
-      <c r="H48" s="39"/>
-      <c r="I48" s="39"/>
-      <c r="J48" s="39"/>
-      <c r="K48" s="39"/>
-      <c r="L48" s="39"/>
-      <c r="M48" s="39"/>
-      <c r="N48" s="39"/>
-      <c r="O48" s="39"/>
-      <c r="P48" s="39"/>
-      <c r="Q48" s="39"/>
-      <c r="R48" s="39"/>
-      <c r="S48" s="39"/>
-      <c r="T48" s="39"/>
-      <c r="U48" s="40"/>
+      <c r="C48" s="45"/>
+      <c r="D48" s="45"/>
+      <c r="E48" s="45"/>
+      <c r="F48" s="45"/>
+      <c r="G48" s="45"/>
+      <c r="H48" s="45"/>
+      <c r="I48" s="45"/>
+      <c r="J48" s="45"/>
+      <c r="K48" s="45"/>
+      <c r="L48" s="45"/>
+      <c r="M48" s="45"/>
+      <c r="N48" s="45"/>
+      <c r="O48" s="45"/>
+      <c r="P48" s="45"/>
+      <c r="Q48" s="45"/>
+      <c r="R48" s="45"/>
+      <c r="S48" s="45"/>
+      <c r="T48" s="45"/>
+      <c r="U48" s="46"/>
     </row>
     <row r="49" spans="1:21">
       <c r="A49" s="13" t="s">
@@ -4453,26 +4450,26 @@
       <c r="C49" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D49" s="44" t="s">
+      <c r="D49" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="E49" s="39"/>
-      <c r="F49" s="39"/>
-      <c r="G49" s="39"/>
-      <c r="H49" s="39"/>
-      <c r="I49" s="39"/>
-      <c r="J49" s="39"/>
-      <c r="K49" s="39"/>
-      <c r="L49" s="39"/>
-      <c r="M49" s="39"/>
-      <c r="N49" s="39"/>
-      <c r="O49" s="39"/>
-      <c r="P49" s="39"/>
-      <c r="Q49" s="39"/>
-      <c r="R49" s="39"/>
-      <c r="S49" s="39"/>
-      <c r="T49" s="39"/>
-      <c r="U49" s="40"/>
+      <c r="E49" s="45"/>
+      <c r="F49" s="45"/>
+      <c r="G49" s="45"/>
+      <c r="H49" s="45"/>
+      <c r="I49" s="45"/>
+      <c r="J49" s="45"/>
+      <c r="K49" s="45"/>
+      <c r="L49" s="45"/>
+      <c r="M49" s="45"/>
+      <c r="N49" s="45"/>
+      <c r="O49" s="45"/>
+      <c r="P49" s="45"/>
+      <c r="Q49" s="45"/>
+      <c r="R49" s="45"/>
+      <c r="S49" s="45"/>
+      <c r="T49" s="45"/>
+      <c r="U49" s="46"/>
     </row>
     <row r="50" spans="1:21" ht="15" thickBot="1">
       <c r="A50" s="13"/>
@@ -4485,50 +4482,50 @@
       <c r="D50" s="38" t="s">
         <v>345</v>
       </c>
-      <c r="E50" s="39"/>
-      <c r="F50" s="39"/>
-      <c r="G50" s="39"/>
-      <c r="H50" s="39"/>
-      <c r="I50" s="39"/>
-      <c r="J50" s="39"/>
-      <c r="K50" s="39"/>
-      <c r="L50" s="39"/>
-      <c r="M50" s="39"/>
-      <c r="N50" s="39"/>
-      <c r="O50" s="39"/>
-      <c r="P50" s="39"/>
-      <c r="Q50" s="39"/>
-      <c r="R50" s="39"/>
-      <c r="S50" s="39"/>
-      <c r="T50" s="39"/>
-      <c r="U50" s="40"/>
+      <c r="E50" s="45"/>
+      <c r="F50" s="45"/>
+      <c r="G50" s="45"/>
+      <c r="H50" s="45"/>
+      <c r="I50" s="45"/>
+      <c r="J50" s="45"/>
+      <c r="K50" s="45"/>
+      <c r="L50" s="45"/>
+      <c r="M50" s="45"/>
+      <c r="N50" s="45"/>
+      <c r="O50" s="45"/>
+      <c r="P50" s="45"/>
+      <c r="Q50" s="45"/>
+      <c r="R50" s="45"/>
+      <c r="S50" s="45"/>
+      <c r="T50" s="45"/>
+      <c r="U50" s="46"/>
     </row>
     <row r="51" spans="1:21">
       <c r="A51" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B51" s="41" t="s">
+      <c r="B51" s="39" t="s">
         <v>346</v>
       </c>
-      <c r="C51" s="42"/>
-      <c r="D51" s="42"/>
-      <c r="E51" s="42"/>
-      <c r="F51" s="42"/>
-      <c r="G51" s="42"/>
-      <c r="H51" s="42"/>
-      <c r="I51" s="42"/>
-      <c r="J51" s="42"/>
-      <c r="K51" s="42"/>
-      <c r="L51" s="42"/>
-      <c r="M51" s="42"/>
-      <c r="N51" s="42"/>
-      <c r="O51" s="42"/>
-      <c r="P51" s="42"/>
-      <c r="Q51" s="42"/>
-      <c r="R51" s="42"/>
-      <c r="S51" s="42"/>
-      <c r="T51" s="42"/>
-      <c r="U51" s="43"/>
+      <c r="C51" s="43"/>
+      <c r="D51" s="43"/>
+      <c r="E51" s="43"/>
+      <c r="F51" s="43"/>
+      <c r="G51" s="43"/>
+      <c r="H51" s="43"/>
+      <c r="I51" s="43"/>
+      <c r="J51" s="43"/>
+      <c r="K51" s="43"/>
+      <c r="L51" s="43"/>
+      <c r="M51" s="43"/>
+      <c r="N51" s="43"/>
+      <c r="O51" s="43"/>
+      <c r="P51" s="43"/>
+      <c r="Q51" s="43"/>
+      <c r="R51" s="43"/>
+      <c r="S51" s="43"/>
+      <c r="T51" s="43"/>
+      <c r="U51" s="44"/>
     </row>
     <row r="52" spans="1:21">
       <c r="A52" s="15" t="s">
@@ -4537,25 +4534,25 @@
       <c r="B52" s="38" t="s">
         <v>347</v>
       </c>
-      <c r="C52" s="39"/>
-      <c r="D52" s="39"/>
-      <c r="E52" s="39"/>
-      <c r="F52" s="39"/>
-      <c r="G52" s="39"/>
-      <c r="H52" s="39"/>
-      <c r="I52" s="39"/>
-      <c r="J52" s="39"/>
-      <c r="K52" s="39"/>
-      <c r="L52" s="39"/>
-      <c r="M52" s="39"/>
-      <c r="N52" s="39"/>
-      <c r="O52" s="39"/>
-      <c r="P52" s="39"/>
-      <c r="Q52" s="39"/>
-      <c r="R52" s="39"/>
-      <c r="S52" s="39"/>
-      <c r="T52" s="39"/>
-      <c r="U52" s="40"/>
+      <c r="C52" s="45"/>
+      <c r="D52" s="45"/>
+      <c r="E52" s="45"/>
+      <c r="F52" s="45"/>
+      <c r="G52" s="45"/>
+      <c r="H52" s="45"/>
+      <c r="I52" s="45"/>
+      <c r="J52" s="45"/>
+      <c r="K52" s="45"/>
+      <c r="L52" s="45"/>
+      <c r="M52" s="45"/>
+      <c r="N52" s="45"/>
+      <c r="O52" s="45"/>
+      <c r="P52" s="45"/>
+      <c r="Q52" s="45"/>
+      <c r="R52" s="45"/>
+      <c r="S52" s="45"/>
+      <c r="T52" s="45"/>
+      <c r="U52" s="46"/>
     </row>
     <row r="53" spans="1:21">
       <c r="A53" s="15" t="s">
@@ -4951,28 +4948,28 @@
       <c r="A68" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="B68" s="41" t="s">
+      <c r="B68" s="39" t="s">
         <v>375</v>
       </c>
-      <c r="C68" s="42"/>
-      <c r="D68" s="42"/>
-      <c r="E68" s="42"/>
-      <c r="F68" s="42"/>
-      <c r="G68" s="42"/>
-      <c r="H68" s="42"/>
-      <c r="I68" s="42"/>
-      <c r="J68" s="42"/>
-      <c r="K68" s="42"/>
-      <c r="L68" s="42"/>
-      <c r="M68" s="42"/>
-      <c r="N68" s="42"/>
-      <c r="O68" s="42"/>
-      <c r="P68" s="42"/>
-      <c r="Q68" s="42"/>
-      <c r="R68" s="42"/>
-      <c r="S68" s="42"/>
-      <c r="T68" s="42"/>
-      <c r="U68" s="43"/>
+      <c r="C68" s="43"/>
+      <c r="D68" s="43"/>
+      <c r="E68" s="43"/>
+      <c r="F68" s="43"/>
+      <c r="G68" s="43"/>
+      <c r="H68" s="43"/>
+      <c r="I68" s="43"/>
+      <c r="J68" s="43"/>
+      <c r="K68" s="43"/>
+      <c r="L68" s="43"/>
+      <c r="M68" s="43"/>
+      <c r="N68" s="43"/>
+      <c r="O68" s="43"/>
+      <c r="P68" s="43"/>
+      <c r="Q68" s="43"/>
+      <c r="R68" s="43"/>
+      <c r="S68" s="43"/>
+      <c r="T68" s="43"/>
+      <c r="U68" s="44"/>
     </row>
     <row r="69" spans="1:21">
       <c r="A69" s="13" t="s">
@@ -4981,25 +4978,25 @@
       <c r="B69" s="38" t="s">
         <v>376</v>
       </c>
-      <c r="C69" s="39"/>
-      <c r="D69" s="39"/>
-      <c r="E69" s="39"/>
-      <c r="F69" s="39"/>
-      <c r="G69" s="39"/>
-      <c r="H69" s="39"/>
-      <c r="I69" s="39"/>
-      <c r="J69" s="39"/>
-      <c r="K69" s="39"/>
-      <c r="L69" s="39"/>
-      <c r="M69" s="39"/>
-      <c r="N69" s="39"/>
-      <c r="O69" s="39"/>
-      <c r="P69" s="39"/>
-      <c r="Q69" s="39"/>
-      <c r="R69" s="39"/>
-      <c r="S69" s="39"/>
-      <c r="T69" s="39"/>
-      <c r="U69" s="40"/>
+      <c r="C69" s="45"/>
+      <c r="D69" s="45"/>
+      <c r="E69" s="45"/>
+      <c r="F69" s="45"/>
+      <c r="G69" s="45"/>
+      <c r="H69" s="45"/>
+      <c r="I69" s="45"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="45"/>
+      <c r="L69" s="45"/>
+      <c r="M69" s="45"/>
+      <c r="N69" s="45"/>
+      <c r="O69" s="45"/>
+      <c r="P69" s="45"/>
+      <c r="Q69" s="45"/>
+      <c r="R69" s="45"/>
+      <c r="S69" s="45"/>
+      <c r="T69" s="45"/>
+      <c r="U69" s="46"/>
     </row>
     <row r="70" spans="1:21">
       <c r="A70" s="13" t="s">
@@ -5011,26 +5008,26 @@
       <c r="C70" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D70" s="44" t="s">
+      <c r="D70" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="E70" s="39"/>
-      <c r="F70" s="39"/>
-      <c r="G70" s="39"/>
-      <c r="H70" s="39"/>
-      <c r="I70" s="39"/>
-      <c r="J70" s="39"/>
-      <c r="K70" s="39"/>
-      <c r="L70" s="39"/>
-      <c r="M70" s="39"/>
-      <c r="N70" s="39"/>
-      <c r="O70" s="39"/>
-      <c r="P70" s="39"/>
-      <c r="Q70" s="39"/>
-      <c r="R70" s="39"/>
-      <c r="S70" s="39"/>
-      <c r="T70" s="39"/>
-      <c r="U70" s="40"/>
+      <c r="E70" s="45"/>
+      <c r="F70" s="45"/>
+      <c r="G70" s="45"/>
+      <c r="H70" s="45"/>
+      <c r="I70" s="45"/>
+      <c r="J70" s="45"/>
+      <c r="K70" s="45"/>
+      <c r="L70" s="45"/>
+      <c r="M70" s="45"/>
+      <c r="N70" s="45"/>
+      <c r="O70" s="45"/>
+      <c r="P70" s="45"/>
+      <c r="Q70" s="45"/>
+      <c r="R70" s="45"/>
+      <c r="S70" s="45"/>
+      <c r="T70" s="45"/>
+      <c r="U70" s="46"/>
     </row>
     <row r="71" spans="1:21" ht="15" thickBot="1">
       <c r="A71" s="13"/>
@@ -5043,50 +5040,50 @@
       <c r="D71" s="38" t="s">
         <v>345</v>
       </c>
-      <c r="E71" s="39"/>
-      <c r="F71" s="39"/>
-      <c r="G71" s="39"/>
-      <c r="H71" s="39"/>
-      <c r="I71" s="39"/>
-      <c r="J71" s="39"/>
-      <c r="K71" s="39"/>
-      <c r="L71" s="39"/>
-      <c r="M71" s="39"/>
-      <c r="N71" s="39"/>
-      <c r="O71" s="39"/>
-      <c r="P71" s="39"/>
-      <c r="Q71" s="39"/>
-      <c r="R71" s="39"/>
-      <c r="S71" s="39"/>
-      <c r="T71" s="39"/>
-      <c r="U71" s="40"/>
+      <c r="E71" s="45"/>
+      <c r="F71" s="45"/>
+      <c r="G71" s="45"/>
+      <c r="H71" s="45"/>
+      <c r="I71" s="45"/>
+      <c r="J71" s="45"/>
+      <c r="K71" s="45"/>
+      <c r="L71" s="45"/>
+      <c r="M71" s="45"/>
+      <c r="N71" s="45"/>
+      <c r="O71" s="45"/>
+      <c r="P71" s="45"/>
+      <c r="Q71" s="45"/>
+      <c r="R71" s="45"/>
+      <c r="S71" s="45"/>
+      <c r="T71" s="45"/>
+      <c r="U71" s="46"/>
     </row>
     <row r="72" spans="1:21">
       <c r="A72" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B72" s="41" t="s">
+      <c r="B72" s="39" t="s">
         <v>378</v>
       </c>
-      <c r="C72" s="42"/>
-      <c r="D72" s="42"/>
-      <c r="E72" s="42"/>
-      <c r="F72" s="42"/>
-      <c r="G72" s="42"/>
-      <c r="H72" s="42"/>
-      <c r="I72" s="42"/>
-      <c r="J72" s="42"/>
-      <c r="K72" s="42"/>
-      <c r="L72" s="42"/>
-      <c r="M72" s="42"/>
-      <c r="N72" s="42"/>
-      <c r="O72" s="42"/>
-      <c r="P72" s="42"/>
-      <c r="Q72" s="42"/>
-      <c r="R72" s="42"/>
-      <c r="S72" s="42"/>
-      <c r="T72" s="42"/>
-      <c r="U72" s="43"/>
+      <c r="C72" s="43"/>
+      <c r="D72" s="43"/>
+      <c r="E72" s="43"/>
+      <c r="F72" s="43"/>
+      <c r="G72" s="43"/>
+      <c r="H72" s="43"/>
+      <c r="I72" s="43"/>
+      <c r="J72" s="43"/>
+      <c r="K72" s="43"/>
+      <c r="L72" s="43"/>
+      <c r="M72" s="43"/>
+      <c r="N72" s="43"/>
+      <c r="O72" s="43"/>
+      <c r="P72" s="43"/>
+      <c r="Q72" s="43"/>
+      <c r="R72" s="43"/>
+      <c r="S72" s="43"/>
+      <c r="T72" s="43"/>
+      <c r="U72" s="44"/>
     </row>
     <row r="73" spans="1:21">
       <c r="A73" s="15" t="s">
@@ -5095,25 +5092,25 @@
       <c r="B73" s="38" t="s">
         <v>379</v>
       </c>
-      <c r="C73" s="39"/>
-      <c r="D73" s="39"/>
-      <c r="E73" s="39"/>
-      <c r="F73" s="39"/>
-      <c r="G73" s="39"/>
-      <c r="H73" s="39"/>
-      <c r="I73" s="39"/>
-      <c r="J73" s="39"/>
-      <c r="K73" s="39"/>
-      <c r="L73" s="39"/>
-      <c r="M73" s="39"/>
-      <c r="N73" s="39"/>
-      <c r="O73" s="39"/>
-      <c r="P73" s="39"/>
-      <c r="Q73" s="39"/>
-      <c r="R73" s="39"/>
-      <c r="S73" s="39"/>
-      <c r="T73" s="39"/>
-      <c r="U73" s="40"/>
+      <c r="C73" s="45"/>
+      <c r="D73" s="45"/>
+      <c r="E73" s="45"/>
+      <c r="F73" s="45"/>
+      <c r="G73" s="45"/>
+      <c r="H73" s="45"/>
+      <c r="I73" s="45"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="45"/>
+      <c r="L73" s="45"/>
+      <c r="M73" s="45"/>
+      <c r="N73" s="45"/>
+      <c r="O73" s="45"/>
+      <c r="P73" s="45"/>
+      <c r="Q73" s="45"/>
+      <c r="R73" s="45"/>
+      <c r="S73" s="45"/>
+      <c r="T73" s="45"/>
+      <c r="U73" s="46"/>
     </row>
     <row r="74" spans="1:21">
       <c r="A74" s="15" t="s">
@@ -5437,28 +5434,28 @@
       <c r="A89" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="B89" s="41" t="s">
+      <c r="B89" s="39" t="s">
         <v>387</v>
       </c>
-      <c r="C89" s="42"/>
-      <c r="D89" s="42"/>
-      <c r="E89" s="42"/>
-      <c r="F89" s="42"/>
-      <c r="G89" s="42"/>
-      <c r="H89" s="42"/>
-      <c r="I89" s="42"/>
-      <c r="J89" s="42"/>
-      <c r="K89" s="42"/>
-      <c r="L89" s="42"/>
-      <c r="M89" s="42"/>
-      <c r="N89" s="42"/>
-      <c r="O89" s="42"/>
-      <c r="P89" s="42"/>
-      <c r="Q89" s="42"/>
-      <c r="R89" s="42"/>
-      <c r="S89" s="42"/>
-      <c r="T89" s="42"/>
-      <c r="U89" s="43"/>
+      <c r="C89" s="43"/>
+      <c r="D89" s="43"/>
+      <c r="E89" s="43"/>
+      <c r="F89" s="43"/>
+      <c r="G89" s="43"/>
+      <c r="H89" s="43"/>
+      <c r="I89" s="43"/>
+      <c r="J89" s="43"/>
+      <c r="K89" s="43"/>
+      <c r="L89" s="43"/>
+      <c r="M89" s="43"/>
+      <c r="N89" s="43"/>
+      <c r="O89" s="43"/>
+      <c r="P89" s="43"/>
+      <c r="Q89" s="43"/>
+      <c r="R89" s="43"/>
+      <c r="S89" s="43"/>
+      <c r="T89" s="43"/>
+      <c r="U89" s="44"/>
     </row>
     <row r="90" spans="1:21">
       <c r="A90" s="13" t="s">
@@ -5467,25 +5464,25 @@
       <c r="B90" s="38" t="s">
         <v>388</v>
       </c>
-      <c r="C90" s="39"/>
-      <c r="D90" s="39"/>
-      <c r="E90" s="39"/>
-      <c r="F90" s="39"/>
-      <c r="G90" s="39"/>
-      <c r="H90" s="39"/>
-      <c r="I90" s="39"/>
-      <c r="J90" s="39"/>
-      <c r="K90" s="39"/>
-      <c r="L90" s="39"/>
-      <c r="M90" s="39"/>
-      <c r="N90" s="39"/>
-      <c r="O90" s="39"/>
-      <c r="P90" s="39"/>
-      <c r="Q90" s="39"/>
-      <c r="R90" s="39"/>
-      <c r="S90" s="39"/>
-      <c r="T90" s="39"/>
-      <c r="U90" s="40"/>
+      <c r="C90" s="45"/>
+      <c r="D90" s="45"/>
+      <c r="E90" s="45"/>
+      <c r="F90" s="45"/>
+      <c r="G90" s="45"/>
+      <c r="H90" s="45"/>
+      <c r="I90" s="45"/>
+      <c r="J90" s="45"/>
+      <c r="K90" s="45"/>
+      <c r="L90" s="45"/>
+      <c r="M90" s="45"/>
+      <c r="N90" s="45"/>
+      <c r="O90" s="45"/>
+      <c r="P90" s="45"/>
+      <c r="Q90" s="45"/>
+      <c r="R90" s="45"/>
+      <c r="S90" s="45"/>
+      <c r="T90" s="45"/>
+      <c r="U90" s="46"/>
     </row>
     <row r="91" spans="1:21">
       <c r="A91" s="13" t="s">
@@ -5497,26 +5494,26 @@
       <c r="C91" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D91" s="44" t="s">
+      <c r="D91" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="E91" s="39"/>
-      <c r="F91" s="39"/>
-      <c r="G91" s="39"/>
-      <c r="H91" s="39"/>
-      <c r="I91" s="39"/>
-      <c r="J91" s="39"/>
-      <c r="K91" s="39"/>
-      <c r="L91" s="39"/>
-      <c r="M91" s="39"/>
-      <c r="N91" s="39"/>
-      <c r="O91" s="39"/>
-      <c r="P91" s="39"/>
-      <c r="Q91" s="39"/>
-      <c r="R91" s="39"/>
-      <c r="S91" s="39"/>
-      <c r="T91" s="39"/>
-      <c r="U91" s="40"/>
+      <c r="E91" s="45"/>
+      <c r="F91" s="45"/>
+      <c r="G91" s="45"/>
+      <c r="H91" s="45"/>
+      <c r="I91" s="45"/>
+      <c r="J91" s="45"/>
+      <c r="K91" s="45"/>
+      <c r="L91" s="45"/>
+      <c r="M91" s="45"/>
+      <c r="N91" s="45"/>
+      <c r="O91" s="45"/>
+      <c r="P91" s="45"/>
+      <c r="Q91" s="45"/>
+      <c r="R91" s="45"/>
+      <c r="S91" s="45"/>
+      <c r="T91" s="45"/>
+      <c r="U91" s="46"/>
     </row>
     <row r="92" spans="1:21" ht="15" thickBot="1">
       <c r="A92" s="13"/>
@@ -5529,50 +5526,50 @@
       <c r="D92" s="38" t="s">
         <v>345</v>
       </c>
-      <c r="E92" s="39"/>
-      <c r="F92" s="39"/>
-      <c r="G92" s="39"/>
-      <c r="H92" s="39"/>
-      <c r="I92" s="39"/>
-      <c r="J92" s="39"/>
-      <c r="K92" s="39"/>
-      <c r="L92" s="39"/>
-      <c r="M92" s="39"/>
-      <c r="N92" s="39"/>
-      <c r="O92" s="39"/>
-      <c r="P92" s="39"/>
-      <c r="Q92" s="39"/>
-      <c r="R92" s="39"/>
-      <c r="S92" s="39"/>
-      <c r="T92" s="39"/>
-      <c r="U92" s="40"/>
+      <c r="E92" s="45"/>
+      <c r="F92" s="45"/>
+      <c r="G92" s="45"/>
+      <c r="H92" s="45"/>
+      <c r="I92" s="45"/>
+      <c r="J92" s="45"/>
+      <c r="K92" s="45"/>
+      <c r="L92" s="45"/>
+      <c r="M92" s="45"/>
+      <c r="N92" s="45"/>
+      <c r="O92" s="45"/>
+      <c r="P92" s="45"/>
+      <c r="Q92" s="45"/>
+      <c r="R92" s="45"/>
+      <c r="S92" s="45"/>
+      <c r="T92" s="45"/>
+      <c r="U92" s="46"/>
     </row>
     <row r="93" spans="1:21">
       <c r="A93" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B93" s="41" t="s">
+      <c r="B93" s="39" t="s">
         <v>390</v>
       </c>
-      <c r="C93" s="42"/>
-      <c r="D93" s="42"/>
-      <c r="E93" s="42"/>
-      <c r="F93" s="42"/>
-      <c r="G93" s="42"/>
-      <c r="H93" s="42"/>
-      <c r="I93" s="42"/>
-      <c r="J93" s="42"/>
-      <c r="K93" s="42"/>
-      <c r="L93" s="42"/>
-      <c r="M93" s="42"/>
-      <c r="N93" s="42"/>
-      <c r="O93" s="42"/>
-      <c r="P93" s="42"/>
-      <c r="Q93" s="42"/>
-      <c r="R93" s="42"/>
-      <c r="S93" s="42"/>
-      <c r="T93" s="42"/>
-      <c r="U93" s="43"/>
+      <c r="C93" s="43"/>
+      <c r="D93" s="43"/>
+      <c r="E93" s="43"/>
+      <c r="F93" s="43"/>
+      <c r="G93" s="43"/>
+      <c r="H93" s="43"/>
+      <c r="I93" s="43"/>
+      <c r="J93" s="43"/>
+      <c r="K93" s="43"/>
+      <c r="L93" s="43"/>
+      <c r="M93" s="43"/>
+      <c r="N93" s="43"/>
+      <c r="O93" s="43"/>
+      <c r="P93" s="43"/>
+      <c r="Q93" s="43"/>
+      <c r="R93" s="43"/>
+      <c r="S93" s="43"/>
+      <c r="T93" s="43"/>
+      <c r="U93" s="44"/>
     </row>
     <row r="94" spans="1:21">
       <c r="A94" s="15" t="s">
@@ -5581,25 +5578,25 @@
       <c r="B94" s="38" t="s">
         <v>391</v>
       </c>
-      <c r="C94" s="39"/>
-      <c r="D94" s="39"/>
-      <c r="E94" s="39"/>
-      <c r="F94" s="39"/>
-      <c r="G94" s="39"/>
-      <c r="H94" s="39"/>
-      <c r="I94" s="39"/>
-      <c r="J94" s="39"/>
-      <c r="K94" s="39"/>
-      <c r="L94" s="39"/>
-      <c r="M94" s="39"/>
-      <c r="N94" s="39"/>
-      <c r="O94" s="39"/>
-      <c r="P94" s="39"/>
-      <c r="Q94" s="39"/>
-      <c r="R94" s="39"/>
-      <c r="S94" s="39"/>
-      <c r="T94" s="39"/>
-      <c r="U94" s="40"/>
+      <c r="C94" s="45"/>
+      <c r="D94" s="45"/>
+      <c r="E94" s="45"/>
+      <c r="F94" s="45"/>
+      <c r="G94" s="45"/>
+      <c r="H94" s="45"/>
+      <c r="I94" s="45"/>
+      <c r="J94" s="45"/>
+      <c r="K94" s="45"/>
+      <c r="L94" s="45"/>
+      <c r="M94" s="45"/>
+      <c r="N94" s="45"/>
+      <c r="O94" s="45"/>
+      <c r="P94" s="45"/>
+      <c r="Q94" s="45"/>
+      <c r="R94" s="45"/>
+      <c r="S94" s="45"/>
+      <c r="T94" s="45"/>
+      <c r="U94" s="46"/>
     </row>
     <row r="95" spans="1:21">
       <c r="A95" s="15" t="s">
@@ -5938,6 +5935,24 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="D92:U92"/>
+    <mergeCell ref="B93:U93"/>
+    <mergeCell ref="B94:U94"/>
+    <mergeCell ref="B72:U72"/>
+    <mergeCell ref="B73:U73"/>
+    <mergeCell ref="B89:U89"/>
+    <mergeCell ref="B90:U90"/>
+    <mergeCell ref="D91:U91"/>
+    <mergeCell ref="B52:U52"/>
+    <mergeCell ref="B68:U68"/>
+    <mergeCell ref="B69:U69"/>
+    <mergeCell ref="D70:U70"/>
+    <mergeCell ref="D71:U71"/>
+    <mergeCell ref="B47:U47"/>
+    <mergeCell ref="B48:U48"/>
+    <mergeCell ref="D49:U49"/>
+    <mergeCell ref="D50:U50"/>
+    <mergeCell ref="B51:U51"/>
     <mergeCell ref="B31:U31"/>
     <mergeCell ref="D7:U7"/>
     <mergeCell ref="B8:U8"/>
@@ -5952,24 +5967,6 @@
     <mergeCell ref="D28:U28"/>
     <mergeCell ref="D29:U29"/>
     <mergeCell ref="B30:U30"/>
-    <mergeCell ref="B47:U47"/>
-    <mergeCell ref="B48:U48"/>
-    <mergeCell ref="D49:U49"/>
-    <mergeCell ref="D50:U50"/>
-    <mergeCell ref="B51:U51"/>
-    <mergeCell ref="B52:U52"/>
-    <mergeCell ref="B68:U68"/>
-    <mergeCell ref="B69:U69"/>
-    <mergeCell ref="D70:U70"/>
-    <mergeCell ref="D71:U71"/>
-    <mergeCell ref="D92:U92"/>
-    <mergeCell ref="B93:U93"/>
-    <mergeCell ref="B94:U94"/>
-    <mergeCell ref="B72:U72"/>
-    <mergeCell ref="B73:U73"/>
-    <mergeCell ref="B89:U89"/>
-    <mergeCell ref="B90:U90"/>
-    <mergeCell ref="D91:U91"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
@@ -5991,24 +5988,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
     </row>
     <row r="4" spans="1:6" ht="27.6">
       <c r="A4" s="25" t="s">
@@ -6157,24 +6154,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
     </row>
     <row r="4" spans="1:6" ht="27.6">
       <c r="A4" s="25" t="s">
